--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260915.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260915.xlsx
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>3,401,000</t>
+          <t>1,983,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,983,288</t>
+          <t>3,401,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>310,672</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>310,672</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>573,000</t>
+          <t>136,921</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>136,921</t>
+          <t>573,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>762,000</t>
+          <t>5,670,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,670,000</t>
+          <t>762,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>928,659</t>
+          <t>1,186,441</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,186,441</t>
+          <t>928,659</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>2,573,703</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2,573,703</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,171,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>2,171,107</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,174,076</t>
+          <t>317,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>317,000</t>
+          <t>1,174,076</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>797,000</t>
+          <t>769,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>4,915,956</t>
+          <t>288,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>769,000</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>288,000</t>
+          <t>797,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>4,915,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
